--- a/artfynd/S 2962-2025 artfynd.xlsx
+++ b/artfynd/S 2962-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY132"/>
+  <dimension ref="A1:AZ132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -771,6 +776,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75733753</t>
         </is>
       </c>
     </row>
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111858164</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127757530</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1095,6 +1115,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128078967</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1196,6 +1221,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128198719</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1295,6 +1325,11 @@
       <c r="AY7" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75733754</t>
         </is>
       </c>
     </row>
@@ -1403,6 +1438,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111857896</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1504,6 +1544,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111858079</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1605,6 +1650,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111858123</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1706,6 +1756,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111858180</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1807,6 +1862,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127109096</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1908,6 +1968,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96601417</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2017,6 +2082,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106807772</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2118,6 +2188,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111857908</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2225,6 +2300,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128078981</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2332,6 +2412,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848077</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2438,6 +2523,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210293</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2547,6 +2637,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127757550</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2654,6 +2749,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128078930</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2760,6 +2860,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210273</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2866,6 +2971,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96368120</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2968,6 +3078,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73531608</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3070,6 +3185,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96601419</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3177,6 +3297,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128079581</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3284,6 +3409,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96368718</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3393,6 +3523,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129140168</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3507,6 +3642,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96195923</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3613,6 +3753,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111858193</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3737,6 +3882,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128790932</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3849,6 +3999,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848015</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3956,6 +4111,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848037</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4073,6 +4233,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128885641</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4179,6 +4344,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129063100</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4285,6 +4455,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129063121</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4396,6 +4571,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129093169</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4502,6 +4682,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210288</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4616,6 +4801,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96359762</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4725,6 +4915,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128391573</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4829,6 +5024,11 @@
       <c r="AY40" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88151817</t>
         </is>
       </c>
     </row>
@@ -4938,6 +5138,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96495719</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5035,6 +5240,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73531607</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5132,6 +5342,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75729864</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5251,6 +5466,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96195872</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5357,6 +5577,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96368287</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5463,6 +5688,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96368288</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5568,6 +5798,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103795155</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5669,6 +5904,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111857910</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5778,6 +6018,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128391590</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5885,6 +6130,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128883572</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5991,6 +6241,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129063085</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6090,6 +6345,11 @@
       <c r="AY52" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75733751</t>
         </is>
       </c>
     </row>
@@ -6198,6 +6458,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96196204</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6312,6 +6577,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96333890</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6418,6 +6688,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96368721</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6518,6 +6793,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67774436</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6627,6 +6907,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128391603</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6733,6 +7018,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210286</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6839,6 +7129,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210289</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6936,6 +7231,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73531610</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7042,6 +7342,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96368095</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7143,6 +7448,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75733748</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7244,6 +7554,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75733752</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7350,6 +7665,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88151679</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7456,6 +7776,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88456083</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7570,6 +7895,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96196048</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7684,6 +8014,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96196148</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7798,6 +8133,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96334081</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7904,6 +8244,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96359789</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8017,6 +8362,11 @@
       <c r="AY70" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96368475</t>
         </is>
       </c>
     </row>
@@ -8125,6 +8475,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129063126</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8226,6 +8581,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129140169</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8327,6 +8687,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75733756</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8433,6 +8798,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88455942</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8552,6 +8922,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96195891</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8658,6 +9033,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96368204</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8764,6 +9144,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96368205</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8870,6 +9255,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96368206</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8967,6 +9357,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73531609</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9074,6 +9469,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128883216</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9185,6 +9585,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129093023</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9291,6 +9696,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210280</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9392,6 +9802,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111858111</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9493,6 +9908,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111858199</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9603,6 +10023,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127109681</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9710,6 +10135,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128790320</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9817,6 +10247,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88151497</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9924,6 +10359,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88151498</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10038,6 +10478,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96195935</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10144,6 +10589,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96196200</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10250,6 +10700,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96359793</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10357,6 +10812,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128078988</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10458,6 +10918,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128198738</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10567,6 +11032,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128391581</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10687,6 +11157,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128883162</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10792,6 +11267,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794689</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10894,6 +11374,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130694998</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11018,6 +11503,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128885794</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11124,6 +11614,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210281</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11236,6 +11731,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128847662</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11348,6 +11848,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128883545</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11454,6 +11959,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88151450</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11558,6 +12068,11 @@
       <c r="AY103" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88455941</t>
         </is>
       </c>
     </row>
@@ -11662,6 +12177,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128198749</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11768,6 +12288,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210287</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11874,6 +12399,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88151855</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11980,6 +12510,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88151856</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12086,6 +12621,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210291</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12192,6 +12732,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87880395</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12298,6 +12843,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88151813</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12404,6 +12954,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88151814</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12510,6 +13065,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88151816</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12616,6 +13176,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88456157</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12722,6 +13287,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88456158</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12826,6 +13396,11 @@
       <c r="AY115" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88456159</t>
         </is>
       </c>
     </row>
@@ -12935,6 +13510,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96195962</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13050,6 +13630,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96196137</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13167,6 +13752,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128784726</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13274,6 +13864,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128884679</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13390,6 +13985,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87880223</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13492,6 +14092,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88455930</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13593,6 +14198,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75733747</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13703,6 +14313,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87880408</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13807,6 +14422,11 @@
       <c r="AY124" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96368336</t>
         </is>
       </c>
     </row>
@@ -13915,6 +14535,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111858152</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14016,6 +14641,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127109636</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14117,6 +14747,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128198743</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14223,6 +14858,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111857904</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14330,6 +14970,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128078934</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14444,6 +15089,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96359797</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14555,6 +15205,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128079275</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14662,8 +15317,146 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210275</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 2962-2025 artfynd.xlsx
+++ b/artfynd/S 2962-2025 artfynd.xlsx
@@ -3308,7 +3308,7 @@
         <v>136106654</v>
       </c>
       <c r="B26" t="n">
-        <v>97948</v>
+        <v>97949</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>136106530</v>
       </c>
       <c r="B53" t="n">
-        <v>91834</v>
+        <v>91835</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>136104030</v>
       </c>
       <c r="B109" t="n">
-        <v>99271</v>
+        <v>99272</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12768,7 +12768,7 @@
         <v>136106670</v>
       </c>
       <c r="B110" t="n">
-        <v>98314</v>
+        <v>98315</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12880,7 +12880,7 @@
         <v>136106545</v>
       </c>
       <c r="B111" t="n">
-        <v>108387</v>
+        <v>108389</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>136106660</v>
       </c>
       <c r="B112" t="n">
-        <v>108387</v>
+        <v>108389</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>136106552</v>
       </c>
       <c r="B115" t="n">
-        <v>106308</v>
+        <v>106310</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>136106673</v>
       </c>
       <c r="B116" t="n">
-        <v>106308</v>
+        <v>106310</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>136104024</v>
       </c>
       <c r="B129" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15033,7 +15033,7 @@
         <v>136104040</v>
       </c>
       <c r="B130" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15149,7 +15149,7 @@
         <v>136106695</v>
       </c>
       <c r="B131" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>136104037</v>
       </c>
       <c r="B133" t="n">
-        <v>101404</v>
+        <v>101406</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         <v>136106667</v>
       </c>
       <c r="B134" t="n">
-        <v>101423</v>
+        <v>101425</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16846,7 +16846,7 @@
         <v>136104021</v>
       </c>
       <c r="B146" t="n">
-        <v>93365</v>
+        <v>93366</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>

--- a/artfynd/S 2962-2025 artfynd.xlsx
+++ b/artfynd/S 2962-2025 artfynd.xlsx
@@ -3308,7 +3308,7 @@
         <v>136106654</v>
       </c>
       <c r="B26" t="n">
-        <v>97949</v>
+        <v>97950</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>136106530</v>
       </c>
       <c r="B53" t="n">
-        <v>91835</v>
+        <v>91836</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>136104030</v>
       </c>
       <c r="B109" t="n">
-        <v>99272</v>
+        <v>99273</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12768,7 +12768,7 @@
         <v>136106670</v>
       </c>
       <c r="B110" t="n">
-        <v>98315</v>
+        <v>98316</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12880,7 +12880,7 @@
         <v>136106545</v>
       </c>
       <c r="B111" t="n">
-        <v>108389</v>
+        <v>108390</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>136106660</v>
       </c>
       <c r="B112" t="n">
-        <v>108389</v>
+        <v>108390</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>136106552</v>
       </c>
       <c r="B115" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>136106673</v>
       </c>
       <c r="B116" t="n">
-        <v>106310</v>
+        <v>106311</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>136104024</v>
       </c>
       <c r="B129" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15033,7 +15033,7 @@
         <v>136104040</v>
       </c>
       <c r="B130" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15149,7 +15149,7 @@
         <v>136106695</v>
       </c>
       <c r="B131" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>136104037</v>
       </c>
       <c r="B133" t="n">
-        <v>101406</v>
+        <v>101407</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         <v>136106667</v>
       </c>
       <c r="B134" t="n">
-        <v>101425</v>
+        <v>101426</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16846,7 +16846,7 @@
         <v>136104021</v>
       </c>
       <c r="B146" t="n">
-        <v>93366</v>
+        <v>93367</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>

--- a/artfynd/S 2962-2025 artfynd.xlsx
+++ b/artfynd/S 2962-2025 artfynd.xlsx
@@ -3308,7 +3308,7 @@
         <v>136106654</v>
       </c>
       <c r="B26" t="n">
-        <v>97950</v>
+        <v>97951</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>136106530</v>
       </c>
       <c r="B53" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -11616,7 +11616,7 @@
         <v>136106833</v>
       </c>
       <c r="B100" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>136104030</v>
       </c>
       <c r="B109" t="n">
-        <v>99273</v>
+        <v>99274</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12768,7 +12768,7 @@
         <v>136106670</v>
       </c>
       <c r="B110" t="n">
-        <v>98316</v>
+        <v>98317</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12865,7 +12865,7 @@
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
+          <t>Toni Berglund, Michael Andersson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
@@ -12880,7 +12880,7 @@
         <v>136106545</v>
       </c>
       <c r="B111" t="n">
-        <v>108390</v>
+        <v>108391</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>136106660</v>
       </c>
       <c r="B112" t="n">
-        <v>108390</v>
+        <v>108391</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
+          <t>Toni Berglund, Michael Andersson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
@@ -13334,7 +13334,7 @@
         <v>136106552</v>
       </c>
       <c r="B115" t="n">
-        <v>106311</v>
+        <v>106312</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>136106673</v>
       </c>
       <c r="B116" t="n">
-        <v>106311</v>
+        <v>106312</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13543,7 +13543,7 @@
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
+          <t>Toni Berglund, Michael Andersson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
@@ -14912,7 +14912,7 @@
         <v>136104024</v>
       </c>
       <c r="B129" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15033,7 +15033,7 @@
         <v>136104040</v>
       </c>
       <c r="B130" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15149,7 +15149,7 @@
         <v>136106695</v>
       </c>
       <c r="B131" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>136104037</v>
       </c>
       <c r="B133" t="n">
-        <v>101407</v>
+        <v>101408</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         <v>136106667</v>
       </c>
       <c r="B134" t="n">
-        <v>101426</v>
+        <v>101427</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15611,7 +15611,7 @@
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
+          <t>Toni Berglund, Michael Andersson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
@@ -16846,7 +16846,7 @@
         <v>136104021</v>
       </c>
       <c r="B146" t="n">
-        <v>93367</v>
+        <v>93368</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>

--- a/artfynd/S 2962-2025 artfynd.xlsx
+++ b/artfynd/S 2962-2025 artfynd.xlsx
@@ -3308,7 +3308,7 @@
         <v>136106654</v>
       </c>
       <c r="B26" t="n">
-        <v>97951</v>
+        <v>97957</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>136106530</v>
       </c>
       <c r="B53" t="n">
-        <v>91837</v>
+        <v>91843</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -11616,7 +11616,7 @@
         <v>136106833</v>
       </c>
       <c r="B100" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>136104030</v>
       </c>
       <c r="B109" t="n">
-        <v>99274</v>
+        <v>99280</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12768,7 +12768,7 @@
         <v>136106670</v>
       </c>
       <c r="B110" t="n">
-        <v>98317</v>
+        <v>98323</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12865,7 +12865,7 @@
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Toni Berglund, Michael Andersson</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
@@ -12880,7 +12880,7 @@
         <v>136106545</v>
       </c>
       <c r="B111" t="n">
-        <v>108391</v>
+        <v>108397</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>136106660</v>
       </c>
       <c r="B112" t="n">
-        <v>108391</v>
+        <v>108397</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Toni Berglund, Michael Andersson</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
@@ -13334,7 +13334,7 @@
         <v>136106552</v>
       </c>
       <c r="B115" t="n">
-        <v>106312</v>
+        <v>106318</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>136106673</v>
       </c>
       <c r="B116" t="n">
-        <v>106312</v>
+        <v>106318</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13543,7 +13543,7 @@
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Toni Berglund, Michael Andersson</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
@@ -14912,7 +14912,7 @@
         <v>136104024</v>
       </c>
       <c r="B129" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15033,7 +15033,7 @@
         <v>136104040</v>
       </c>
       <c r="B130" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15149,7 +15149,7 @@
         <v>136106695</v>
       </c>
       <c r="B131" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>136104037</v>
       </c>
       <c r="B133" t="n">
-        <v>101408</v>
+        <v>101414</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         <v>136106667</v>
       </c>
       <c r="B134" t="n">
-        <v>101427</v>
+        <v>101433</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15611,7 +15611,7 @@
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Toni Berglund, Michael Andersson</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
@@ -16846,7 +16846,7 @@
         <v>136104021</v>
       </c>
       <c r="B146" t="n">
-        <v>93368</v>
+        <v>93374</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>

--- a/artfynd/S 2962-2025 artfynd.xlsx
+++ b/artfynd/S 2962-2025 artfynd.xlsx
@@ -3308,7 +3308,7 @@
         <v>136106654</v>
       </c>
       <c r="B26" t="n">
-        <v>97957</v>
+        <v>97958</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>136106530</v>
       </c>
       <c r="B53" t="n">
-        <v>91843</v>
+        <v>91844</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -11616,7 +11616,7 @@
         <v>136106833</v>
       </c>
       <c r="B100" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>136104030</v>
       </c>
       <c r="B109" t="n">
-        <v>99280</v>
+        <v>99281</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12768,7 +12768,7 @@
         <v>136106670</v>
       </c>
       <c r="B110" t="n">
-        <v>98323</v>
+        <v>98324</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12880,7 +12880,7 @@
         <v>136106545</v>
       </c>
       <c r="B111" t="n">
-        <v>108397</v>
+        <v>108398</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>136106660</v>
       </c>
       <c r="B112" t="n">
-        <v>108397</v>
+        <v>108398</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>136106552</v>
       </c>
       <c r="B115" t="n">
-        <v>106318</v>
+        <v>106319</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>136106673</v>
       </c>
       <c r="B116" t="n">
-        <v>106318</v>
+        <v>106319</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>136104024</v>
       </c>
       <c r="B129" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15033,7 +15033,7 @@
         <v>136104040</v>
       </c>
       <c r="B130" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15149,7 +15149,7 @@
         <v>136106695</v>
       </c>
       <c r="B131" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>136104037</v>
       </c>
       <c r="B133" t="n">
-        <v>101414</v>
+        <v>101415</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         <v>136106667</v>
       </c>
       <c r="B134" t="n">
-        <v>101433</v>
+        <v>101434</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16846,7 +16846,7 @@
         <v>136104021</v>
       </c>
       <c r="B146" t="n">
-        <v>93374</v>
+        <v>93375</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
